--- a/projeto_maturacao/data/raw/mate_choice.xlsx
+++ b/projeto_maturacao/data/raw/mate_choice.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23801"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PC\Documents\GitHub\tese_cap3\projeto_maturacao\data\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\GitHub\nuptial_manuscript\projeto_maturacao\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF6A579A-2253-44A8-87F6-19711800C0BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C869D94-B217-4A9E-A2A8-A6FED0627B67}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="10">
   <si>
     <t>ID</t>
   </si>
@@ -46,12 +46,6 @@
   </si>
   <si>
     <t>dark</t>
-  </si>
-  <si>
-    <t>obs</t>
-  </si>
-  <si>
-    <t>no_video</t>
   </si>
   <si>
     <t>experimento</t>
@@ -379,16 +373,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G97"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:F97"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="4" max="4" width="11.42578125" customWidth="1"/>
-    <col min="5" max="5" width="17.7109375" customWidth="1"/>
-    <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.42578125" customWidth="1"/>
+    <col min="4" max="4" width="11.453125" customWidth="1"/>
+    <col min="5" max="5" width="17.7265625" customWidth="1"/>
+    <col min="6" max="6" width="10.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -402,16 +395,13 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="G1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -425,13 +415,13 @@
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -445,13 +435,13 @@
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -465,13 +455,13 @@
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F4" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>2</v>
       </c>
@@ -485,13 +475,13 @@
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>3</v>
       </c>
@@ -505,13 +495,13 @@
         <v>0</v>
       </c>
       <c r="E6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F6" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>3</v>
       </c>
@@ -525,13 +515,13 @@
         <v>0</v>
       </c>
       <c r="E7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F7" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>4</v>
       </c>
@@ -545,13 +535,13 @@
         <v>0</v>
       </c>
       <c r="E8" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>4</v>
       </c>
@@ -565,13 +555,13 @@
         <v>0</v>
       </c>
       <c r="E9" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F9" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>5</v>
       </c>
@@ -585,13 +575,13 @@
         <v>1</v>
       </c>
       <c r="E10" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F10" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>5</v>
       </c>
@@ -605,13 +595,13 @@
         <v>1</v>
       </c>
       <c r="E11" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F11" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>6</v>
       </c>
@@ -625,13 +615,13 @@
         <v>1</v>
       </c>
       <c r="E12" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F12" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>6</v>
       </c>
@@ -645,13 +635,13 @@
         <v>1</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F13" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>7</v>
       </c>
@@ -665,13 +655,13 @@
         <v>0</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F14" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>7</v>
       </c>
@@ -685,13 +675,13 @@
         <v>0</v>
       </c>
       <c r="E15" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F15" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>8</v>
       </c>
@@ -705,13 +695,13 @@
         <v>2</v>
       </c>
       <c r="E16" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F16" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>8</v>
       </c>
@@ -725,13 +715,13 @@
         <v>2</v>
       </c>
       <c r="E17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F17" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>9</v>
       </c>
@@ -745,13 +735,13 @@
         <v>0</v>
       </c>
       <c r="E18" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F18" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>9</v>
       </c>
@@ -765,13 +755,13 @@
         <v>0</v>
       </c>
       <c r="E19" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F19" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>10</v>
       </c>
@@ -785,13 +775,13 @@
         <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F20" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>10</v>
       </c>
@@ -805,13 +795,13 @@
         <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F21" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>11</v>
       </c>
@@ -825,13 +815,13 @@
         <v>0</v>
       </c>
       <c r="E22" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F22" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>11</v>
       </c>
@@ -845,13 +835,13 @@
         <v>0</v>
       </c>
       <c r="E23" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>12</v>
       </c>
@@ -865,13 +855,13 @@
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F24" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>12</v>
       </c>
@@ -885,13 +875,13 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F25" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>13</v>
       </c>
@@ -905,16 +895,13 @@
         <v>0</v>
       </c>
       <c r="E26" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F26" s="1">
         <v>45583</v>
       </c>
-      <c r="G26" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>13</v>
       </c>
@@ -928,16 +915,13 @@
         <v>0</v>
       </c>
       <c r="E27" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F27" s="1">
         <v>45583</v>
       </c>
-      <c r="G27" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>14</v>
       </c>
@@ -951,13 +935,13 @@
         <v>0</v>
       </c>
       <c r="E28" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F28" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>14</v>
       </c>
@@ -971,13 +955,13 @@
         <v>0</v>
       </c>
       <c r="E29" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F29" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>15</v>
       </c>
@@ -991,13 +975,13 @@
         <v>1</v>
       </c>
       <c r="E30" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F30" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>15</v>
       </c>
@@ -1011,13 +995,13 @@
         <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F31" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>16</v>
       </c>
@@ -1031,13 +1015,13 @@
         <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F32" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>16</v>
       </c>
@@ -1051,13 +1035,13 @@
         <v>1</v>
       </c>
       <c r="E33" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F33" s="1">
         <v>45583</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>17</v>
       </c>
@@ -1071,13 +1055,13 @@
         <v>3</v>
       </c>
       <c r="E34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F34" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>17</v>
       </c>
@@ -1091,13 +1075,13 @@
         <v>3</v>
       </c>
       <c r="E35" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F35" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>18</v>
       </c>
@@ -1111,13 +1095,13 @@
         <v>5</v>
       </c>
       <c r="E36" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F36" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>18</v>
       </c>
@@ -1131,13 +1115,13 @@
         <v>5</v>
       </c>
       <c r="E37" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F37" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>19</v>
       </c>
@@ -1151,13 +1135,13 @@
         <v>1</v>
       </c>
       <c r="E38" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F38" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>19</v>
       </c>
@@ -1171,13 +1155,13 @@
         <v>0</v>
       </c>
       <c r="E39" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F39" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>20</v>
       </c>
@@ -1191,13 +1175,13 @@
         <v>0</v>
       </c>
       <c r="E40" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F40" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>20</v>
       </c>
@@ -1211,13 +1195,13 @@
         <v>0</v>
       </c>
       <c r="E41" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F41" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>21</v>
       </c>
@@ -1231,13 +1215,13 @@
         <v>0</v>
       </c>
       <c r="E42" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F42" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>21</v>
       </c>
@@ -1251,13 +1235,13 @@
         <v>0</v>
       </c>
       <c r="E43" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F43" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>22</v>
       </c>
@@ -1271,13 +1255,13 @@
         <v>0</v>
       </c>
       <c r="E44" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F44" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>22</v>
       </c>
@@ -1291,13 +1275,13 @@
         <v>0</v>
       </c>
       <c r="E45" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F45" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>23</v>
       </c>
@@ -1311,13 +1295,13 @@
         <v>0</v>
       </c>
       <c r="E46" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F46" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>23</v>
       </c>
@@ -1331,13 +1315,13 @@
         <v>0</v>
       </c>
       <c r="E47" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F47" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>24</v>
       </c>
@@ -1351,13 +1335,13 @@
         <v>0</v>
       </c>
       <c r="E48" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F48" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>24</v>
       </c>
@@ -1371,13 +1355,13 @@
         <v>0</v>
       </c>
       <c r="E49" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F49" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>25</v>
       </c>
@@ -1391,13 +1375,13 @@
         <v>0</v>
       </c>
       <c r="E50" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F50" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>25</v>
       </c>
@@ -1411,13 +1395,13 @@
         <v>0</v>
       </c>
       <c r="E51" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F51" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>26</v>
       </c>
@@ -1431,13 +1415,13 @@
         <v>2</v>
       </c>
       <c r="E52" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F52" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>26</v>
       </c>
@@ -1451,13 +1435,13 @@
         <v>2</v>
       </c>
       <c r="E53" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F53" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>27</v>
       </c>
@@ -1471,13 +1455,13 @@
         <v>0</v>
       </c>
       <c r="E54" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F54" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>27</v>
       </c>
@@ -1491,13 +1475,13 @@
         <v>0</v>
       </c>
       <c r="E55" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F55" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>28</v>
       </c>
@@ -1511,13 +1495,13 @@
         <v>0</v>
       </c>
       <c r="E56" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F56" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>28</v>
       </c>
@@ -1531,13 +1515,13 @@
         <v>0</v>
       </c>
       <c r="E57" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F57" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>29</v>
       </c>
@@ -1551,13 +1535,13 @@
         <v>0</v>
       </c>
       <c r="E58" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F58" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>29</v>
       </c>
@@ -1571,13 +1555,13 @@
         <v>0</v>
       </c>
       <c r="E59" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F59" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>30</v>
       </c>
@@ -1591,13 +1575,13 @@
         <v>2</v>
       </c>
       <c r="E60" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F60" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>30</v>
       </c>
@@ -1611,13 +1595,13 @@
         <v>2</v>
       </c>
       <c r="E61" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F61" s="1">
         <v>45584</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>31</v>
       </c>
@@ -1631,13 +1615,13 @@
         <v>0</v>
       </c>
       <c r="E62" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F62" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>31</v>
       </c>
@@ -1651,13 +1635,13 @@
         <v>0</v>
       </c>
       <c r="E63" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F63" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>32</v>
       </c>
@@ -1671,13 +1655,13 @@
         <v>1</v>
       </c>
       <c r="E64" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F64" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>32</v>
       </c>
@@ -1691,13 +1675,13 @@
         <v>1</v>
       </c>
       <c r="E65" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F65" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>33</v>
       </c>
@@ -1711,13 +1695,13 @@
         <v>0</v>
       </c>
       <c r="E66" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F66" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>33</v>
       </c>
@@ -1731,13 +1715,13 @@
         <v>0</v>
       </c>
       <c r="E67" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F67" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>34</v>
       </c>
@@ -1751,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="E68" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F68" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>34</v>
       </c>
@@ -1771,13 +1755,13 @@
         <v>1</v>
       </c>
       <c r="E69" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F69" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>35</v>
       </c>
@@ -1791,13 +1775,13 @@
         <v>0</v>
       </c>
       <c r="E70" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F70" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>35</v>
       </c>
@@ -1811,13 +1795,13 @@
         <v>0</v>
       </c>
       <c r="E71" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F71" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>36</v>
       </c>
@@ -1831,13 +1815,13 @@
         <v>1</v>
       </c>
       <c r="E72" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F72" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>36</v>
       </c>
@@ -1851,13 +1835,13 @@
         <v>1</v>
       </c>
       <c r="E73" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F73" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>37</v>
       </c>
@@ -1871,13 +1855,13 @@
         <v>0</v>
       </c>
       <c r="E74" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F74" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="75" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>37</v>
       </c>
@@ -1891,13 +1875,13 @@
         <v>0</v>
       </c>
       <c r="E75" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F75" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="76" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>38</v>
       </c>
@@ -1911,13 +1895,13 @@
         <v>0</v>
       </c>
       <c r="E76" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F76" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>38</v>
       </c>
@@ -1931,13 +1915,13 @@
         <v>0</v>
       </c>
       <c r="E77" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F77" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>39</v>
       </c>
@@ -1951,13 +1935,13 @@
         <v>1</v>
       </c>
       <c r="E78" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F78" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>39</v>
       </c>
@@ -1971,13 +1955,13 @@
         <v>1</v>
       </c>
       <c r="E79" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F79" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>40</v>
       </c>
@@ -1991,13 +1975,13 @@
         <v>0</v>
       </c>
       <c r="E80" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F80" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="81" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>40</v>
       </c>
@@ -2011,13 +1995,13 @@
         <v>0</v>
       </c>
       <c r="E81" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F81" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>41</v>
       </c>
@@ -2031,13 +2015,13 @@
         <v>1</v>
       </c>
       <c r="E82" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F82" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="83" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>41</v>
       </c>
@@ -2051,13 +2035,13 @@
         <v>1</v>
       </c>
       <c r="E83" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F83" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="84" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>42</v>
       </c>
@@ -2071,13 +2055,13 @@
         <v>1</v>
       </c>
       <c r="E84" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F84" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="85" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>42</v>
       </c>
@@ -2091,13 +2075,13 @@
         <v>1</v>
       </c>
       <c r="E85" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F85" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="86" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>43</v>
       </c>
@@ -2111,13 +2095,13 @@
         <v>0</v>
       </c>
       <c r="E86" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F86" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="87" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>43</v>
       </c>
@@ -2131,13 +2115,13 @@
         <v>0</v>
       </c>
       <c r="E87" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F87" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="88" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>44</v>
       </c>
@@ -2151,13 +2135,13 @@
         <v>1</v>
       </c>
       <c r="E88" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F88" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="89" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>44</v>
       </c>
@@ -2171,13 +2155,13 @@
         <v>1</v>
       </c>
       <c r="E89" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F89" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="90" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>45</v>
       </c>
@@ -2191,13 +2175,13 @@
         <v>0</v>
       </c>
       <c r="E90" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F90" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="91" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>45</v>
       </c>
@@ -2211,13 +2195,13 @@
         <v>0</v>
       </c>
       <c r="E91" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F91" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="92" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>46</v>
       </c>
@@ -2231,13 +2215,13 @@
         <v>1</v>
       </c>
       <c r="E92" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F92" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="93" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>46</v>
       </c>
@@ -2251,13 +2235,13 @@
         <v>1</v>
       </c>
       <c r="E93" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F93" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="94" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>47</v>
       </c>
@@ -2271,13 +2255,13 @@
         <v>1</v>
       </c>
       <c r="E94" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F94" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="95" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>47</v>
       </c>
@@ -2291,13 +2275,13 @@
         <v>1</v>
       </c>
       <c r="E95" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F95" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="96" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>48</v>
       </c>
@@ -2311,13 +2295,13 @@
         <v>0</v>
       </c>
       <c r="E96" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F96" s="1">
         <v>45585</v>
       </c>
     </row>
-    <row r="97" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A97">
         <v>48</v>
       </c>
@@ -2331,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="E97" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F97" s="1">
         <v>45585</v>
